--- a/artfynd/A 43141-2022 artfynd.xlsx
+++ b/artfynd/A 43141-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43141-2022 artfynd.xlsx
+++ b/artfynd/A 43141-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>7229159</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510216.1352387329</v>
+        <v>510216</v>
       </c>
       <c r="R2" t="n">
-        <v>6953856.004786827</v>
+        <v>6953856</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,19 +757,9 @@
           <t>2013-07-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67840361</v>
+        <v>67840354</v>
       </c>
       <c r="B3" t="n">
-        <v>97040</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -851,14 +831,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sidsjö, Östboda / 0,8 km NV /, Djupnäsviken, Jmt</t>
+          <t>Sidsjö, Östboda / 0,65 km NV /, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510024.1466398594</v>
+        <v>510147</v>
       </c>
       <c r="R3" t="n">
-        <v>6953986.630338349</v>
+        <v>6953938</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,24 +868,14 @@
           <t>2017-06-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-06-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>42 ex inom 20 m kant av grusväg. Intill grusås nära Sidsjöns strand. Öppet läge.</t>
+          <t>20 ex inom 25 m kant av grusväg, längs vägens båda sidor. På tallås nära Sidsjöns strand. Glest tallbestånd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +889,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Vägkant grusväg intill grusås, öppet läge</t>
+          <t>Vägkant grusväg på tallås nära sjö. Glest tallbestånd.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,6 +904,122 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>67840361</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99869</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222356</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Frösöstarr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carex pediformis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>C. A. Mey.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sidsjö, Östboda / 0,8 km NV /, Djupnäsviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>510024</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6953987</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-06-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-06-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>42 ex inom 20 m kant av grusväg. Intill grusås nära Sidsjöns strand. Öppet läge.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägkant grusväg intill grusås, öppet läge</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43141-2022 artfynd.xlsx
+++ b/artfynd/A 43141-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7229159</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67840354</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,8 +1035,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67840361</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>